--- a/examples/HO_SO_CAU_KM19_529/260920_TDTC_CaXe_CaMay_DauDiezel_Cau_Km19+529.080.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/260920_TDTC_CaXe_CaMay_DauDiezel_Cau_Km19+529.080.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_TongHop_CaXe_CaMay_MMTB" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KeHoach_Dau_Diezel" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_KeHoach_NhanLuc" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_DoiChieu_BocTach_Km19" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_DoiChieu_BocTach" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/examples/HO_SO_CAU_KM19_529/260920_TDTC_CaXe_CaMay_DauDiezel_Cau_Km19+529.080.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/260920_TDTC_CaXe_CaMay_DauDiezel_Cau_Km19+529.080.xlsx
@@ -755,7 +755,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:GC70"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -38435,7 +38435,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -39122,7 +39122,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -39741,7 +39741,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -40196,7 +40196,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>

--- a/examples/HO_SO_CAU_KM19_529/260920_TDTC_CaXe_CaMay_DauDiezel_Cau_Km19+529.080.xlsx
+++ b/examples/HO_SO_CAU_KM19_529/260920_TDTC_CaXe_CaMay_DauDiezel_Cau_Km19+529.080.xlsx
@@ -755,7 +755,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:GC70"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -38435,7 +38435,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -39122,7 +39122,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -39741,7 +39741,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -40196,7 +40196,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
